--- a/tests/criminal_first_instance_cases_2026_06_01_to_2026_06_10.xlsx
+++ b/tests/criminal_first_instance_cases_2026_06_01_to_2026_06_10.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 17:00:17</t>
+          <t>2026-06-10 20:37:35</t>
         </is>
       </c>
     </row>
